--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -737,10 +737,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>fsum_notes</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fsum_note_lines</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MSS;Global Payments Solutions;Global Trade Solutions;Credit and Lending;HIF;CMA Net;Other Revenue;ECLs (ex Notables);Direct Costs (ex VP);Variable Pay (VP);Indirect Costs;Customers and Banks Deposits (PE);Loans and Advances to Customers and Banks (PE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>show_greeting</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>N</t>
         </is>

--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>accH1,accH2,accH3,accH4,accH5,cgL2,country</t>
+          <t>accH1,accH2,accH3,accH4,accH5,prodH2,prodH3,prodH4,cgL2,country</t>
         </is>
       </c>
     </row>
@@ -3137,14 +3137,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
@@ -3186,6 +3186,756 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Markets</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Foreign Exchange</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Foreign Exchange|FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Markets</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Rates</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Markets</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Credit Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Markets</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Equities</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Equities</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Securities Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Securities Services</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Custody</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Custody</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Securities Services</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fund Administration</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fund Administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Securities Services</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Issuer Services</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Issuer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Global Payments Solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Global Payments Solutions</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Payments and Cash Management</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Payments and Cash Management|PCM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Global Payments Solutions</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Liquidity Management</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Liquidity Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Global Payments Solutions</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Commercial Cards</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Commercial Cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Global Trade Solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Global Trade Solutions</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Documentary Trade</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Documentary Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Global Trade Solutions</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Receivables Finance</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Receivables Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>B19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Global Trade Solutions</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Guarantees</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Guarantees</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Credit and Lending</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>B21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Credit and Lending</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Corporate Lending</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Corporate Lending</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Credit and Lending</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Structured Finance</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Structured Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>B23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Credit and Lending</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Portfolio Management</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Portfolio Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>B24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Capital Markets and Advisory</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Capital Markets and Advisory</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Debt Capital Markets</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Debt Capital Markets|DCM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Capital Markets and Advisory</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Equity Capital Markets</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Equity Capital Markets|ECM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Capital Markets and Advisory</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Advisory</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Advisory</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HIF</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>HIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Non product aligned</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Non product aligned</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -749,22 +749,34 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fsum_note_lines</t>
+          <t>commentary_disclaimer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MSS;Global Payments Solutions;Global Trade Solutions;Credit and Lending;HIF;CMA Net;Other Revenue;ECLs (ex Notables);Direct Costs (ex VP);Variable Pay (VP);Indirect Costs;Customers and Banks Deposits (PE);Loans and Advances to Customers and Banks (PE)</t>
+          <t>This CIB Asia &amp; MENAT commentary has been generated from the figures in the file and the commentary document loaded with it. It may be inaccurate and/or incomplete. Review and edit before further use or distribution.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>fsum_note_lines</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MSS;Global Payments Solutions;Global Trade Solutions;Credit and Lending;HIF;CMA Net;Other Revenue;ECLs (ex Notables);Direct Costs (ex VP);Variable Pay (VP);Indirect Costs;Customers and Banks Deposits (PE);Loans and Advances to Customers and Banks (PE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>show_greeting</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>N</t>
         </is>

--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>This CIB Asia &amp; MENAT commentary has been generated from the figures in the file and the commentary document loaded with it. It may be inaccurate and/or incomplete. Review and edit before further use or distribution.</t>
+          <t>This CIB Asia &amp; MENAT commentary has been generated from the figures in the file and the written commentary carried with it. It may be inaccurate and/or incomplete. Review and edit before further use or distribution.</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -14,10 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Views" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labels" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drivers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductHierarchy" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AccountHierarchy" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commentary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductHierarchy" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AccountHierarchy" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,6 +794,816 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Markets</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Foreign Exchange</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Foreign Exchange|FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Markets</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Rates</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Markets</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Credit Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Markets</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Equities</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Equities</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Securities Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Securities Services</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Custody</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Custody</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Securities Services</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fund Administration</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fund Administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Securities Services</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Issuer Services</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Issuer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Global Payments Solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Global Payments Solutions</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Payments and Cash Management</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Payments and Cash Management|PCM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Global Payments Solutions</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Liquidity Management</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Liquidity Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Global Payments Solutions</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Commercial Cards</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Commercial Cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Global Trade Solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Global Trade Solutions</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Documentary Trade</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Documentary Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Global Trade Solutions</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Receivables Finance</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Receivables Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>B19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Global Trade Solutions</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Guarantees</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Guarantees</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Credit and Lending</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>B21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Credit and Lending</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Corporate Lending</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Corporate Lending</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Credit and Lending</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Structured Finance</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Structured Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>B23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Credit and Lending</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Portfolio Management</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Portfolio Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>B24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Capital Markets and Advisory</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Capital Markets and Advisory</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Debt Capital Markets</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Debt Capital Markets|DCM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Capital Markets and Advisory</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Equity Capital Markets</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Equity Capital Markets|ECM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Capital Markets and Advisory</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Advisory</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Advisory</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HIF</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>HIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Non product aligned</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Non product aligned</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1673,7 +2484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2879,262 +3690,103 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>View</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total Revenue (ex Notables)</t>
+          <t>Financial Summary</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>accH3=Total Revenue (ex Notables)</t>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Rates and FX carried the half; deposit margin narrowed broadly as planned.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MSS</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>accH4=MSS</t>
+          <t>Markets and Securities Services</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Rates and FX led the half while Custody stayed soft.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Global Payments Solutions</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>accH4=Global Payments Solutions</t>
+          <t>Global Trade Solutions</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Drawdowns slipped into July - timing, not demand. The pipeline is intact.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Credit and Lending</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>accH4=Credit and Lending</t>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>June closes the half ahead of plan on revenue and behind on costs.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Global Trade Solutions</t>
-        </is>
-      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>accH4=Global Trade Solutions</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>HIF</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>accH4=HIF</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CMA Net</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>accH4=CMA Net</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Other Revenue</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>accH4=Other Revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Banking NII</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>income=Banking NII</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fee and other income</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>income=Fee and other income</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ECLs (ex Notables)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>accH3=ECLs (ex Notables)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Direct Costs (ex VP)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>accH4=Direct Costs (ex VP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Variable Pay (VP)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>accH4=Variable Pay (VP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Indirect Costs</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>accH4=Indirect Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Total Operating Expenses (ex Notables)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>accH3=Total Operating Expenses (ex Notables)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PBT (ex Notables)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>accH2=PBT (ex Notables)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PBT (Reported)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>accH1=PBT (Reported)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Customer Deposits (PE)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>accH2=o/w Customer Deposits (PE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Loans and Advances to Customers (PE)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>accH2=o/w Loans and Advances to Customers (PE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Total RWAs</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>accH1=Total RWAs</t>
+          <t>Global Payments Solutions</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Payments volumes held up well; liquidity margin thinner as rates came off.</t>
         </is>
       </c>
     </row>
@@ -3149,802 +3801,262 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Level 4</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Match</t>
+          <t>Scope</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>Total Revenue (ex Notables)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>accH3=Total Revenue (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>MSS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Markets and Securities Services</t>
+          <t>accH4=MSS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>Global Payments Solutions</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Markets and Securities Services</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Markets</t>
+          <t>accH4=Global Payments Solutions</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>Credit and Lending</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Markets and Securities Services</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Markets</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Foreign Exchange</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Foreign Exchange|FX</t>
+          <t>accH4=Credit and Lending</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B5</t>
+          <t>Global Trade Solutions</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Markets and Securities Services</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Markets</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Rates</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Rates</t>
+          <t>accH4=Global Trade Solutions</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B6</t>
+          <t>HIF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Markets and Securities Services</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Markets</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Credit Trading</t>
+          <t>accH4=HIF</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B7</t>
+          <t>CMA Net</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Markets and Securities Services</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Markets</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Equities</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Equities</t>
+          <t>accH4=CMA Net</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B8</t>
+          <t>Other Revenue</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Markets and Securities Services</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Securities Services</t>
+          <t>accH4=Other Revenue</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B9</t>
+          <t>Banking NII</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Markets and Securities Services</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Securities Services</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Custody</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Custody</t>
+          <t>income=Banking NII</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B10</t>
+          <t>Fee and other income</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Markets and Securities Services</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Securities Services</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Fund Administration</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Fund Administration</t>
+          <t>income=Fee and other income</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>ECLs (ex Notables)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Markets and Securities Services</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Securities Services</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Issuer Services</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Issuer Services</t>
+          <t>accH3=ECLs (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>Direct Costs (ex VP)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Global Payments Solutions</t>
+          <t>accH4=Direct Costs (ex VP)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B13</t>
+          <t>Variable Pay (VP)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Global Payments Solutions</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Payments and Cash Management</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Payments and Cash Management|PCM</t>
+          <t>accH4=Variable Pay (VP)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B14</t>
+          <t>Indirect Costs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Global Payments Solutions</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Liquidity Management</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Liquidity Management</t>
+          <t>accH4=Indirect Costs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B15</t>
+          <t>Total Operating Expenses (ex Notables)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Global Payments Solutions</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Commercial Cards</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Commercial Cards</t>
+          <t>accH3=Total Operating Expenses (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B16</t>
+          <t>PBT (ex Notables)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Global Trade Solutions</t>
+          <t>accH2=PBT (ex Notables)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B17</t>
+          <t>PBT (Reported)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Global Trade Solutions</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Documentary Trade</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Documentary Trade</t>
+          <t>accH1=PBT (Reported)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B18</t>
+          <t>Customer Deposits (PE)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Global Trade Solutions</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Receivables Finance</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Receivables Finance</t>
+          <t>accH2=o/w Customer Deposits (PE)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B19</t>
+          <t>Loans and Advances to Customers (PE)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Global Trade Solutions</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Guarantees</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Guarantees</t>
+          <t>accH2=o/w Loans and Advances to Customers (PE)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B20</t>
+          <t>Total RWAs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Credit and Lending</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>B21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Credit and Lending</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Corporate Lending</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Corporate Lending</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>B22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Credit and Lending</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Structured Finance</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Structured Finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>B23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Credit and Lending</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Portfolio Management</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Portfolio Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>B24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Capital Markets and Advisory</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>B25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Capital Markets and Advisory</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Debt Capital Markets</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Debt Capital Markets|DCM</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>B26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Capital Markets and Advisory</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Equity Capital Markets</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Equity Capital Markets|ECM</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>B27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Capital Markets and Advisory</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Advisory</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Advisory</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>B28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>HIF</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>HIF</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>B29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>B30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Non product aligned</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Non product aligned</t>
+          <t>accH1=Total RWAs</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -780,6 +780,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>variance_periods</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>qtr_py,ytd_tgt,mth_fc,fy_pfc,fy_py,fy_tgt</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductHierarchy" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AccountHierarchy" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CommentaryTemplates" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,13 +40,22 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DB0011"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -60,9 +70,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3339,6 +3350,77 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Exec brief</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>{line} {var} {vs}, led by {drivers}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FP&amp;A detail</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>{line}: {main} against {base} — {varamt} ({varpct}) {vs}. Key movers: {drivers}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>&lt;i&gt;Tokens: {line} {main} {base} {var} {varamt} {varpct} {vs} {basename} {period} {drivers} {month} {quarter} {fy} {ytd}. View blank = every view. Uploaded rows replace the built-in examples wholesale; the reader picks the style on the Management Commentary panel.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -803,6 +803,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>qtr_py,ytd_tgt,mth_fc,fy_pfc,fy_py,fy_tgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>commentary_format</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3368,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3372,7 +3384,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
@@ -3384,37 +3396,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Exec brief</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>Group narrative</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{line} {var} {vs}, led by {drivers}.</t>
+          <t>{line} {var} {vs} across the Group, led by {drivers}.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FP&amp;A detail</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>CIB Global</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CIB Global</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{line}: {main} against {base} — {varamt} ({varpct}) {vs}. Key movers: {drivers}.</t>
+          <t>{scope}: {line} {var} {vs}, led by {drivers}.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Tokens: {line} {main} {base} {var} {varamt} {varpct} {vs} {basename} {period} {drivers} {month} {quarter} {fy} {ytd}. View blank = every view. Uploaded rows replace the built-in examples wholesale; the reader picks the style on the Management Commentary panel.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+          <t>CIB Regional</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CIB Regional</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>{scope}: {line} {var} {vs} across the region, driven by {drivers}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CIB Country</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CIB Country</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>In {scope}, {line} came in at {main}, {var} {vs} on {drivers}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Exec brief</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{line} {var} {vs}, led by {drivers}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FP&amp;A detail</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{line}: {main} against {base} — {varamt} ({varpct}) {vs}. Key movers: {drivers}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>&lt;i&gt;Scope words: Group · Global · Regional · Country, optionally led by a business (IWPB Global) or a place (Singapore). With the style set to Auto — match the scope, the page adopts the best-fitting template as the scope moves; no scoped template defined for a scope means the pack narrative speaks there. A blank scope makes a named style picked by hand.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -817,6 +817,14 @@
           <t>auto</t>
         </is>
       </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>tile_visible</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3467,7 +3475,6 @@
           <t>Exec brief</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>{line} {var} {vs}, led by {drivers}.</t>
@@ -3480,7 +3487,6 @@
           <t>FP&amp;A detail</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>{line}: {main} against {base} — {varamt} ({varpct}) {vs}. Key movers: {drivers}.</t>
@@ -3493,8 +3499,6 @@
           <t>&lt;i&gt;Scope words: Group · Global · Regional · Country, optionally led by a business (IWPB Global) or a place (Singapore). With the style set to Auto — match the scope, the page adopts the best-fitting template as the scope moves; no scoped template defined for a scope means the pack narrative speaks there. A blank scope makes a named style picked by hand.</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -824,7 +824,6 @@
           <t>tile_visible</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3772,7 +3771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3824,6 +3823,30 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>KPIs · CIB lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ingest_title</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ingest TM1 Extract</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ingest_drop</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Drop the TM1 extract here</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -823,6 +823,26 @@
         <is>
           <t>tile_visible</t>
         </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>tile_height</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>tile_min_width</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>124</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>236</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -3791,7 +3791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3867,6 +3867,30 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>Drop the TM1 extract here</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>nav_bizperf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Business performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>nav_comall</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>All commentaries</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -3791,7 +3791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ingest TM1 Extract</t>
+          <t>Ingest TM1 Data Extract</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Drop the TM1 extract here</t>
+          <t>Drop the TM1 data extract here</t>
         </is>
       </c>
     </row>
@@ -3891,6 +3891,18 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>All commentaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>btn_newfile</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ingest TM1 Data Extract</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/CIB_dashboard_config_pack.xlsx
@@ -45,7 +45,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DB0011"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009E1B32"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,10 +75,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3791,20 +3797,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
@@ -3825,84 +3831,300 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nav_fsum</t>
+          <t>nav_custom</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Financial Summary</t>
+          <t>My dashboard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sect_kpis</t>
+          <t>nav_builder</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KPIs · CIB lines</t>
+          <t>Drag &amp; drop charts</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ingest_title</t>
+          <t>nav_query</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ingest TM1 Data Extract</t>
+          <t>Query builder</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ingest_drop</t>
+          <t>nav_assist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Drop the TM1 data extract here</t>
+          <t>MI Assistant</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nav_bizperf</t>
+          <t>nav_sim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Business performance</t>
+          <t>Simulation Assistant</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nav_comall</t>
+          <t>nav_fsum</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>All commentaries</t>
+          <t>Financial Summary</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>nav_comall</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>All commentaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>nav_bizperf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Business performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sect_dashboards</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KPI Dashboards</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sect_config</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sect_period</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sect_comtpl</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Commentary templates</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>btn_newfile</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Ingest TM1 Data Extract</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ingest_title</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ingest TM1 Data Extract</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ingest_drop</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Drop the TM1 data extract here</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>btn_regen</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Regenerate</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>btn_retrieve</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Retrieve</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>lbl_year</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>lbl_ytd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>YTD through</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>lbl_varper</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Variance period</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>lbl_units</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>lbl_scope</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>lbl_tplpick</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Active style</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>dec_eyebrow</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Decisions required</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>dec_title</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Executive decisions</t>
         </is>
       </c>
     </row>
